--- a/Model_data/Universal_primers/primers.xlsx
+++ b/Model_data/Universal_primers/primers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haoyu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F4FCEB-1D67-4391-9295-5FA7801595F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC029F52-87C9-491F-81DA-0EA9AA9ECA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2820" yWindow="1140" windowWidth="23040" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>seq_type</t>
   </si>
@@ -43,24 +43,12 @@
     <t>v_region</t>
   </si>
   <si>
-    <t>27F_338R</t>
-  </si>
-  <si>
     <t>AGAGTTTGATCCTGGCTCAG</t>
   </si>
   <si>
-    <t>TGCTGCCTCCCGTAGGAGT</t>
-  </si>
-  <si>
-    <t>311bp</t>
-  </si>
-  <si>
     <t>PE250</t>
   </si>
   <si>
-    <t>v1v2</t>
-  </si>
-  <si>
     <t>27F_533R</t>
   </si>
   <si>
@@ -121,48 +109,9 @@
     <t>v4v4</t>
   </si>
   <si>
-    <t>787F_1073R</t>
-  </si>
-  <si>
-    <t>ATTAGATACCCYGGTAGTCC</t>
-  </si>
-  <si>
-    <t>ACGAGCTGACGACARCATG</t>
-  </si>
-  <si>
-    <t>286bp</t>
-  </si>
-  <si>
-    <t>v5v6</t>
-  </si>
-  <si>
-    <t>799F_1193R</t>
-  </si>
-  <si>
-    <t>AACMGGATAGATACCCKG</t>
-  </si>
-  <si>
-    <t>ACGTCATCCCCACCTTCC</t>
-  </si>
-  <si>
-    <t>394bp</t>
-  </si>
-  <si>
     <t>v5v7</t>
   </si>
   <si>
-    <t>969F_1406R</t>
-  </si>
-  <si>
-    <t>ACGCGHNRAACCTTACC</t>
-  </si>
-  <si>
-    <t>ACGGGCRGTGWGTRCAA</t>
-  </si>
-  <si>
-    <t>437bp</t>
-  </si>
-  <si>
     <t>v6v8</t>
   </si>
   <si>
@@ -200,18 +149,6 @@
   </si>
   <si>
     <t>492bp</t>
-  </si>
-  <si>
-    <t>939F_1378R</t>
-  </si>
-  <si>
-    <t>GAATTGACGGGGGCCCGCACAAG</t>
-  </si>
-  <si>
-    <t>CGGTGTGTACAAGGCCCGGGAACG</t>
-  </si>
-  <si>
-    <t>439bp</t>
   </si>
   <si>
     <t>bacterial 16S rRNA</t>
@@ -599,13 +536,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -628,280 +565,165 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="G8" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +731,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 B3:G13 B2:G2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 B3:G6 B7:G8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>